--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1278,6 +1278,2789 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128557953</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>541905</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6712022</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128569027</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kroken, Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>542189</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6712176</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128557833</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lerbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>541901</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6712022</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128564663</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92754</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kroken, Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>542256</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6712255</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hallonlik vätska, skarp smak, granskog med närmaste tall 20m bort.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128569151</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97448</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kroken, Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>542189</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6712175</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128569182</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kroken, Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>542185</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6712163</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128558408</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>541940</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6712068</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128568250</v>
+      </c>
+      <c r="B14" t="n">
+        <v>75171</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kroken, Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>542191</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6712201</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128558222</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>541897</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6712013</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Område där eventuellt en och samma individ flyger omkring</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128568775</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kroken, Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>542174</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6712176</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128556581</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58055</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>541919</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6711934</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128557706</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>541902</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6711998</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128567986</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>542207</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6712193</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128557356</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>541909</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6712025</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128569305</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>542178</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6712169</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128568829</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>542203</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6712181</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128569162</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>542197</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6712176</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128568881</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>542179</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6712187</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128563434</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>542106</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6712261</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128557515</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92770</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Kroken, Vika , Torvströmyran, Kroken, Vika , Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>541912</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6712002</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Fem fruktkroppar på en knapp m2. Tyvärr alldeles i närheten av gallrad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128569105</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>542192</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6712166</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128561310</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kroken, Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>541975</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6712087</v>
+      </c>
+      <c r="S28" t="n">
+        <v>30</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128564481</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>542253</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6712239</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>6 st blomstjälkar</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -2711,64 +2711,60 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128567986</v>
+        <v>128557356</v>
       </c>
       <c r="B19" t="n">
-        <v>98571</v>
+        <v>57845</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>542207</v>
+        <v>541909</v>
       </c>
       <c r="R19" t="n">
-        <v>6712193</v>
+        <v>6712025</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2797,7 +2793,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2807,7 +2803,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2816,7 +2812,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2835,60 +2830,64 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128557356</v>
+        <v>128567986</v>
       </c>
       <c r="B20" t="n">
-        <v>57845</v>
+        <v>98571</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541909</v>
+        <v>542207</v>
       </c>
       <c r="R20" t="n">
-        <v>6712025</v>
+        <v>6712193</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2917,7 +2916,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2927,7 +2926,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2936,6 +2935,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3078,7 +3078,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128568829</v>
+        <v>128568723</v>
       </c>
       <c r="B22" t="n">
         <v>98571</v>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3695,60 +3695,60 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128569105</v>
+        <v>128561310</v>
       </c>
       <c r="B27" t="n">
-        <v>98571</v>
+        <v>57845</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>542192</v>
+        <v>541975</v>
       </c>
       <c r="R27" t="n">
-        <v>6712166</v>
+        <v>6712087</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3796,7 +3796,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3815,60 +3814,60 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128561310</v>
+        <v>128569105</v>
       </c>
       <c r="B28" t="n">
-        <v>57845</v>
+        <v>98571</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541975</v>
+        <v>542192</v>
       </c>
       <c r="R28" t="n">
-        <v>6712087</v>
+        <v>6712166</v>
       </c>
       <c r="S28" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3897,7 +3896,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3907,7 +3906,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3916,6 +3915,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -3078,7 +3078,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128568723</v>
+        <v>128568829</v>
       </c>
       <c r="B22" t="n">
         <v>98571</v>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -1283,7 +1283,7 @@
         <v>128557953</v>
       </c>
       <c r="B7" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128569027</v>
       </c>
       <c r="B8" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>128557833</v>
       </c>
       <c r="B9" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128564663</v>
       </c>
       <c r="B10" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>128569151</v>
       </c>
       <c r="B11" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1880,10 +1880,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128569182</v>
+        <v>128558408</v>
       </c>
       <c r="B12" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,19 +1923,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>542185</v>
+        <v>541940</v>
       </c>
       <c r="R12" t="n">
-        <v>6712163</v>
+        <v>6712068</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1964,7 +1966,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1974,7 +1976,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1983,28 +1985,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Åsa Weinberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128558408</v>
+        <v>128569182</v>
       </c>
       <c r="B13" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2044,21 +2047,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541940</v>
+        <v>542185</v>
       </c>
       <c r="R13" t="n">
-        <v>6712068</v>
+        <v>6712163</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2087,7 +2088,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2097,7 +2098,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2106,19 +2107,18 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Åsa Weinberg, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2128,7 +2128,7 @@
         <v>128568250</v>
       </c>
       <c r="B14" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>128558222</v>
       </c>
       <c r="B15" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>128568775</v>
       </c>
       <c r="B16" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>128556581</v>
       </c>
       <c r="B17" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>128557706</v>
       </c>
       <c r="B18" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2711,60 +2711,64 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128557356</v>
+        <v>128567986</v>
       </c>
       <c r="B19" t="n">
-        <v>57845</v>
+        <v>98579</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541909</v>
+        <v>542207</v>
       </c>
       <c r="R19" t="n">
-        <v>6712025</v>
+        <v>6712193</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2793,7 +2797,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2803,7 +2807,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2812,6 +2816,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2830,64 +2835,60 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128567986</v>
+        <v>128557356</v>
       </c>
       <c r="B20" t="n">
-        <v>98571</v>
+        <v>57849</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>542207</v>
+        <v>541909</v>
       </c>
       <c r="R20" t="n">
-        <v>6712193</v>
+        <v>6712025</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2916,7 +2917,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2926,7 +2927,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2935,7 +2936,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>128569305</v>
       </c>
       <c r="B21" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>128568829</v>
       </c>
       <c r="B22" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>128569162</v>
       </c>
       <c r="B23" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>128568881</v>
       </c>
       <c r="B24" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>128563434</v>
       </c>
       <c r="B25" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>128557515</v>
       </c>
       <c r="B26" t="n">
-        <v>92770</v>
+        <v>92776</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3695,60 +3695,60 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128561310</v>
+        <v>128569105</v>
       </c>
       <c r="B27" t="n">
-        <v>57845</v>
+        <v>98579</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541975</v>
+        <v>542192</v>
       </c>
       <c r="R27" t="n">
-        <v>6712087</v>
+        <v>6712166</v>
       </c>
       <c r="S27" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3796,6 +3796,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3814,60 +3815,60 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128569105</v>
+        <v>128561310</v>
       </c>
       <c r="B28" t="n">
-        <v>98571</v>
+        <v>57849</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542192</v>
+        <v>541975</v>
       </c>
       <c r="R28" t="n">
-        <v>6712166</v>
+        <v>6712087</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3896,7 +3897,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3906,7 +3907,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3915,7 +3916,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3937,7 +3937,7 @@
         <v>128564481</v>
       </c>
       <c r="B29" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Åsa Weinberg, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -1283,7 +1283,7 @@
         <v>128557953</v>
       </c>
       <c r="B7" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128569027</v>
       </c>
       <c r="B8" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>128557833</v>
       </c>
       <c r="B9" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128564663</v>
       </c>
       <c r="B10" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>128569151</v>
       </c>
       <c r="B11" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1880,10 +1880,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128558408</v>
+        <v>128569182</v>
       </c>
       <c r="B12" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,21 +1923,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541940</v>
+        <v>542185</v>
       </c>
       <c r="R12" t="n">
-        <v>6712068</v>
+        <v>6712163</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1966,7 +1964,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1976,7 +1974,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1985,29 +1983,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Åsa Weinberg, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128569182</v>
+        <v>128558408</v>
       </c>
       <c r="B13" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,19 +2044,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>542185</v>
+        <v>541940</v>
       </c>
       <c r="R13" t="n">
-        <v>6712163</v>
+        <v>6712068</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2088,7 +2087,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2098,7 +2097,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2107,18 +2106,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Åsa Weinberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2359,7 +2359,7 @@
         <v>128568775</v>
       </c>
       <c r="B16" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>128557706</v>
       </c>
       <c r="B18" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>128567986</v>
       </c>
       <c r="B19" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>128569305</v>
       </c>
       <c r="B21" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3078,10 +3078,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128568829</v>
+        <v>128568723</v>
       </c>
       <c r="B22" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3205,7 +3205,7 @@
         <v>128569162</v>
       </c>
       <c r="B23" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>128568881</v>
       </c>
       <c r="B24" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>128563434</v>
       </c>
       <c r="B25" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>128557515</v>
       </c>
       <c r="B26" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3695,60 +3695,60 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128569105</v>
+        <v>128561310</v>
       </c>
       <c r="B27" t="n">
-        <v>98579</v>
+        <v>57849</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>542192</v>
+        <v>541975</v>
       </c>
       <c r="R27" t="n">
-        <v>6712166</v>
+        <v>6712087</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3796,7 +3796,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3815,60 +3814,60 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128561310</v>
+        <v>128569105</v>
       </c>
       <c r="B28" t="n">
-        <v>57849</v>
+        <v>98585</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541975</v>
+        <v>542192</v>
       </c>
       <c r="R28" t="n">
-        <v>6712087</v>
+        <v>6712166</v>
       </c>
       <c r="S28" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3897,7 +3896,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3907,7 +3906,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3916,6 +3915,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3937,7 +3937,7 @@
         <v>128564481</v>
       </c>
       <c r="B29" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -3695,60 +3695,60 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128561310</v>
+        <v>128569105</v>
       </c>
       <c r="B27" t="n">
-        <v>57849</v>
+        <v>98585</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541975</v>
+        <v>542192</v>
       </c>
       <c r="R27" t="n">
-        <v>6712087</v>
+        <v>6712166</v>
       </c>
       <c r="S27" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3796,6 +3796,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3814,60 +3815,60 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128569105</v>
+        <v>128561310</v>
       </c>
       <c r="B28" t="n">
-        <v>98585</v>
+        <v>57849</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542192</v>
+        <v>541975</v>
       </c>
       <c r="R28" t="n">
-        <v>6712166</v>
+        <v>6712087</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3896,7 +3897,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3906,7 +3907,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3915,7 +3916,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -1283,7 +1283,7 @@
         <v>128557953</v>
       </c>
       <c r="B7" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128569027</v>
       </c>
       <c r="B8" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>128557833</v>
       </c>
       <c r="B9" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128564663</v>
       </c>
       <c r="B10" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>128569151</v>
       </c>
       <c r="B11" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1880,10 +1880,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128569182</v>
+        <v>128558408</v>
       </c>
       <c r="B12" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,19 +1923,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>542185</v>
+        <v>541940</v>
       </c>
       <c r="R12" t="n">
-        <v>6712163</v>
+        <v>6712068</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1964,7 +1966,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1974,7 +1976,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1983,28 +1985,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Åsa Weinberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128558408</v>
+        <v>128569182</v>
       </c>
       <c r="B13" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2044,21 +2047,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541940</v>
+        <v>542185</v>
       </c>
       <c r="R13" t="n">
-        <v>6712068</v>
+        <v>6712163</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2087,7 +2088,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2097,7 +2098,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2106,19 +2107,18 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Åsa Weinberg, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2128,7 +2128,7 @@
         <v>128568250</v>
       </c>
       <c r="B14" t="n">
-        <v>75175</v>
+        <v>75177</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>128568775</v>
       </c>
       <c r="B16" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>128557706</v>
       </c>
       <c r="B18" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>128567986</v>
       </c>
       <c r="B19" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>128569305</v>
       </c>
       <c r="B21" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3078,10 +3078,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128568723</v>
+        <v>128568829</v>
       </c>
       <c r="B22" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3205,7 +3205,7 @@
         <v>128569162</v>
       </c>
       <c r="B23" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>128568881</v>
       </c>
       <c r="B24" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>128563434</v>
       </c>
       <c r="B25" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>128557515</v>
       </c>
       <c r="B26" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>128569105</v>
       </c>
       <c r="B27" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>128564481</v>
       </c>
       <c r="B29" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -1283,7 +1283,7 @@
         <v>128557953</v>
       </c>
       <c r="B7" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128569027</v>
       </c>
       <c r="B8" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>128557833</v>
       </c>
       <c r="B9" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>128558408</v>
       </c>
       <c r="B12" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>128569182</v>
       </c>
       <c r="B13" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>128568775</v>
       </c>
       <c r="B16" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>128557706</v>
       </c>
       <c r="B18" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2711,64 +2711,60 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128567986</v>
+        <v>128557356</v>
       </c>
       <c r="B19" t="n">
-        <v>98588</v>
+        <v>57849</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>542207</v>
+        <v>541909</v>
       </c>
       <c r="R19" t="n">
-        <v>6712193</v>
+        <v>6712025</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2797,7 +2793,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2807,7 +2803,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2816,7 +2812,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2835,60 +2830,64 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128557356</v>
+        <v>128567986</v>
       </c>
       <c r="B20" t="n">
-        <v>57849</v>
+        <v>98591</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541909</v>
+        <v>542207</v>
       </c>
       <c r="R20" t="n">
-        <v>6712025</v>
+        <v>6712193</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2917,7 +2916,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2927,7 +2926,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2936,6 +2935,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>128569305</v>
       </c>
       <c r="B21" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>128568829</v>
       </c>
       <c r="B22" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>128569162</v>
       </c>
       <c r="B23" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>128568881</v>
       </c>
       <c r="B24" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>128563434</v>
       </c>
       <c r="B25" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>128569105</v>
       </c>
       <c r="B27" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>128564481</v>
       </c>
       <c r="B29" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -2711,60 +2711,64 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128557356</v>
+        <v>128567986</v>
       </c>
       <c r="B19" t="n">
-        <v>57849</v>
+        <v>98591</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541909</v>
+        <v>542207</v>
       </c>
       <c r="R19" t="n">
-        <v>6712025</v>
+        <v>6712193</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2793,7 +2797,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2803,7 +2807,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2812,6 +2816,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2830,64 +2835,60 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128567986</v>
+        <v>128557356</v>
       </c>
       <c r="B20" t="n">
-        <v>98591</v>
+        <v>57849</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>542207</v>
+        <v>541909</v>
       </c>
       <c r="R20" t="n">
-        <v>6712193</v>
+        <v>6712025</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2916,7 +2917,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2926,7 +2927,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2935,7 +2936,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3695,60 +3695,60 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128569105</v>
+        <v>128561310</v>
       </c>
       <c r="B27" t="n">
-        <v>98591</v>
+        <v>57849</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>542192</v>
+        <v>541975</v>
       </c>
       <c r="R27" t="n">
-        <v>6712166</v>
+        <v>6712087</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3796,7 +3796,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3815,60 +3814,60 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128561310</v>
+        <v>128569105</v>
       </c>
       <c r="B28" t="n">
-        <v>57849</v>
+        <v>98591</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541975</v>
+        <v>542192</v>
       </c>
       <c r="R28" t="n">
-        <v>6712087</v>
+        <v>6712166</v>
       </c>
       <c r="S28" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3897,7 +3896,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3907,7 +3906,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3916,6 +3915,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -1283,7 +1283,7 @@
         <v>128557953</v>
       </c>
       <c r="B7" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128569027</v>
       </c>
       <c r="B8" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>128557833</v>
       </c>
       <c r="B9" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128564663</v>
       </c>
       <c r="B10" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>128569151</v>
       </c>
       <c r="B11" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>128558408</v>
       </c>
       <c r="B12" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>128569182</v>
       </c>
       <c r="B13" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2232,60 +2232,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128558222</v>
+        <v>128568775</v>
       </c>
       <c r="B15" t="n">
-        <v>57849</v>
+        <v>98592</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541897</v>
+        <v>542174</v>
       </c>
       <c r="R15" t="n">
-        <v>6712013</v>
+        <v>6712176</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2314,7 +2311,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2324,12 +2321,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Område där eventuellt en och samma individ flyger omkring</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2344,69 +2336,72 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Åsa Weinberg, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128568775</v>
+        <v>128558222</v>
       </c>
       <c r="B16" t="n">
-        <v>98591</v>
+        <v>57849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>542174</v>
+        <v>541897</v>
       </c>
       <c r="R16" t="n">
-        <v>6712176</v>
+        <v>6712013</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2435,7 +2430,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2445,7 +2440,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Område där eventuellt en och samma individ flyger omkring</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2460,12 +2460,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Åsa Weinberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2590,7 +2590,7 @@
         <v>128557706</v>
       </c>
       <c r="B18" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2711,64 +2711,60 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128567986</v>
+        <v>128557356</v>
       </c>
       <c r="B19" t="n">
-        <v>98591</v>
+        <v>57849</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>542207</v>
+        <v>541909</v>
       </c>
       <c r="R19" t="n">
-        <v>6712193</v>
+        <v>6712025</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2797,7 +2793,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2807,7 +2803,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2816,7 +2812,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2835,60 +2830,64 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128557356</v>
+        <v>128567986</v>
       </c>
       <c r="B20" t="n">
-        <v>57849</v>
+        <v>98592</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541909</v>
+        <v>542207</v>
       </c>
       <c r="R20" t="n">
-        <v>6712025</v>
+        <v>6712193</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2917,7 +2916,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2927,7 +2926,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2936,6 +2935,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>128569305</v>
       </c>
       <c r="B21" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>128568829</v>
       </c>
       <c r="B22" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>128569162</v>
       </c>
       <c r="B23" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>128568881</v>
       </c>
       <c r="B24" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>128563434</v>
       </c>
       <c r="B25" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>128557515</v>
       </c>
       <c r="B26" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>128569105</v>
       </c>
       <c r="B28" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>128564481</v>
       </c>
       <c r="B29" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1283,7 +1283,7 @@
         <v>128557953</v>
       </c>
       <c r="B7" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128569027</v>
       </c>
       <c r="B8" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>128557833</v>
       </c>
       <c r="B9" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128564663</v>
       </c>
       <c r="B10" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>128569151</v>
       </c>
       <c r="B11" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>128558408</v>
       </c>
       <c r="B12" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>128569182</v>
       </c>
       <c r="B13" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>128568250</v>
       </c>
       <c r="B14" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>128568775</v>
       </c>
       <c r="B15" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>128558222</v>
       </c>
       <c r="B16" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>128556581</v>
       </c>
       <c r="B17" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>128557706</v>
       </c>
       <c r="B18" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>128557356</v>
       </c>
       <c r="B19" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>128567986</v>
       </c>
       <c r="B20" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>128569305</v>
       </c>
       <c r="B21" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>128568829</v>
       </c>
       <c r="B22" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>128569162</v>
       </c>
       <c r="B23" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>128568881</v>
       </c>
       <c r="B24" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>128563434</v>
       </c>
       <c r="B25" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>128557515</v>
       </c>
       <c r="B26" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>128561310</v>
       </c>
       <c r="B27" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>128569105</v>
       </c>
       <c r="B28" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>128564481</v>
       </c>
       <c r="B29" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4060,6 +4060,2526 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128562756</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>542094</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6712276</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 25 bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128827016</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kroken, Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>542101</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6712271</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128556421</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>541936</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6711921</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128829012</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kroken, Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>542184</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6712198</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Minst 17 plantor på några dm 2.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128822696</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kroken, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>542137</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6712159</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128827575</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kroken, Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>542092</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6712254</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor, varav 1 överblommade stängsel.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128827098</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kroken, Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>542101</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6712275</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Cirka 50 plantor varav två överblommade stänglar, påyta om cirka 9,3x1,0 meter.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128828742</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kroken, Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>542181</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6712183</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128830117</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kroken, Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>542160</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6712167</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128827330</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kroken, Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>542092</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6712260</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Minst 50 plantor som växer tätt på en yta om cirka 1x1 meter</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128828662</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kroken, Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>542178</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6712173</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128827353</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kroken, Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>542091</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6712256</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128568945</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kroken, Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>542191</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6712170</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128563445</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kroken, Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>542085</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6712250</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Minst femton friska bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128828897</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kroken, Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>542192</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6712176</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minst 30 ex på cirka 1 m2.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128828808</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kroken, Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>542185</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6712179</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128827283</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>542093</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6712261</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128563536</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kroken, Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>542088</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6712247</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128826691</v>
+      </c>
+      <c r="B48" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>541964</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6712107</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128827411</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Kroken, Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>542092</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6712255</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 14 ex på mindre yta.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128829197</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kroken, Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>542186</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6712207</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Minst 56 plantor på cirka 0,5 m2.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2232,57 +2232,60 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128568775</v>
+        <v>128558222</v>
       </c>
       <c r="B15" t="n">
-        <v>98619</v>
+        <v>57876</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542174</v>
+        <v>541897</v>
       </c>
       <c r="R15" t="n">
-        <v>6712176</v>
+        <v>6712013</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2311,7 +2314,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2321,7 +2324,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Område där eventuellt en och samma individ flyger omkring</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2336,72 +2344,69 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Åsa Weinberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128558222</v>
+        <v>128568775</v>
       </c>
       <c r="B16" t="n">
-        <v>57876</v>
+        <v>98619</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541897</v>
+        <v>542174</v>
       </c>
       <c r="R16" t="n">
-        <v>6712013</v>
+        <v>6712176</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2430,7 +2435,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2440,12 +2445,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Område där eventuellt en och samma individ flyger omkring</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2460,12 +2460,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Åsa Weinberg, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -4063,7 +4063,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128562756</v>
+        <v>128827016</v>
       </c>
       <c r="B30" t="n">
         <v>98619</v>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4101,21 +4101,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>542094</v>
+        <v>542101</v>
       </c>
       <c r="R30" t="n">
-        <v>6712276</v>
+        <v>6712271</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4142,27 +4137,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 25 bladrosetter.</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4182,14 +4172,14 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128827016</v>
+        <v>128562756</v>
       </c>
       <c r="B31" t="n">
         <v>98619</v>
@@ -4219,7 +4209,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4227,16 +4217,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>542101</v>
+        <v>542094</v>
       </c>
       <c r="R31" t="n">
-        <v>6712271</v>
+        <v>6712276</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4263,22 +4258,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Minst 25 bladrosetter.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4538,7 +4538,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128822696</v>
+        <v>128827575</v>
       </c>
       <c r="B34" t="n">
         <v>98619</v>
@@ -4566,21 +4566,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kroken, Falun, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>542137</v>
+        <v>542092</v>
       </c>
       <c r="R34" t="n">
-        <v>6712159</v>
+        <v>6712254</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4607,22 +4612,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor, varav 1 överblommade stängsel.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4631,7 +4641,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4650,7 +4659,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128827575</v>
+        <v>128822696</v>
       </c>
       <c r="B35" t="n">
         <v>98619</v>
@@ -4678,26 +4687,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>542092</v>
+        <v>542137</v>
       </c>
       <c r="R35" t="n">
-        <v>6712254</v>
+        <v>6712159</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4724,27 +4728,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:19</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Minst 30 plantor, varav 1 överblommade stängsel.</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4753,6 +4752,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4771,7 +4771,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128827098</v>
+        <v>128828742</v>
       </c>
       <c r="B36" t="n">
         <v>98619</v>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>542101</v>
+        <v>542181</v>
       </c>
       <c r="R36" t="n">
-        <v>6712275</v>
+        <v>6712183</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4865,12 +4865,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Cirka 50 plantor varav två överblommade stänglar, påyta om cirka 9,3x1,0 meter.</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4897,7 +4892,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128828742</v>
+        <v>128827098</v>
       </c>
       <c r="B37" t="n">
         <v>98619</v>
@@ -4927,7 +4922,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4937,7 +4932,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4946,10 +4941,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>542181</v>
+        <v>542101</v>
       </c>
       <c r="R37" t="n">
-        <v>6712183</v>
+        <v>6712275</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4981,7 +4976,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4991,7 +4986,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Cirka 50 plantor varav två överblommade stänglar, påyta om cirka 9,3x1,0 meter.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5875,7 +5875,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128828808</v>
+        <v>128563536</v>
       </c>
       <c r="B45" t="n">
         <v>98619</v>
@@ -5903,31 +5903,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>542185</v>
+        <v>542088</v>
       </c>
       <c r="R45" t="n">
-        <v>6712179</v>
+        <v>6712247</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5954,22 +5940,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5989,14 +5975,14 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128827283</v>
+        <v>128828808</v>
       </c>
       <c r="B46" t="n">
         <v>98619</v>
@@ -6026,7 +6012,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6041,14 +6027,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542093</v>
+        <v>542185</v>
       </c>
       <c r="R46" t="n">
-        <v>6712261</v>
+        <v>6712179</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6080,7 +6066,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6090,7 +6076,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6117,7 +6103,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128563536</v>
+        <v>128827283</v>
       </c>
       <c r="B47" t="n">
         <v>98619</v>
@@ -6145,17 +6131,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>542088</v>
+        <v>542093</v>
       </c>
       <c r="R47" t="n">
-        <v>6712247</v>
+        <v>6712261</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6182,22 +6182,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6217,52 +6217,66 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128826691</v>
+        <v>128827411</v>
       </c>
       <c r="B48" t="n">
-        <v>5177</v>
+        <v>98619</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541964</v>
+        <v>542092</v>
       </c>
       <c r="R48" t="n">
-        <v>6712107</v>
+        <v>6712255</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6294,7 +6308,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6304,7 +6318,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Minst 14 ex på mindre yta.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6331,59 +6350,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128827411</v>
+        <v>128826691</v>
       </c>
       <c r="B49" t="n">
-        <v>98619</v>
+        <v>5177</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>542092</v>
+        <v>541964</v>
       </c>
       <c r="R49" t="n">
-        <v>6712255</v>
+        <v>6712107</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6415,7 +6420,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6425,12 +6430,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Minst 14 ex på mindre yta.</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6581,6 +6581,130 @@
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128570551</v>
+      </c>
+      <c r="B51" t="n">
+        <v>86842</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>442</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Bullspindling</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cortinarius corrosus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>542013</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6712124</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Jan-Olof Hermansson har utifrån fotona bekräftat arten.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -1283,7 +1283,7 @@
         <v>128557953</v>
       </c>
       <c r="B7" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128569027</v>
       </c>
       <c r="B8" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>128557833</v>
       </c>
       <c r="B9" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128564663</v>
       </c>
       <c r="B10" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>128569151</v>
       </c>
       <c r="B11" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>128558408</v>
       </c>
       <c r="B12" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>128569182</v>
       </c>
       <c r="B13" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>128568250</v>
       </c>
       <c r="B14" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>128568775</v>
       </c>
       <c r="B16" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>128557706</v>
       </c>
       <c r="B18" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>128567986</v>
       </c>
       <c r="B20" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>128569305</v>
       </c>
       <c r="B21" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>128568829</v>
       </c>
       <c r="B22" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>128569162</v>
       </c>
       <c r="B23" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>128568881</v>
       </c>
       <c r="B24" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>128563434</v>
       </c>
       <c r="B25" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>128557515</v>
       </c>
       <c r="B26" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>128569105</v>
       </c>
       <c r="B28" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>128564481</v>
       </c>
       <c r="B29" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>128827016</v>
       </c>
       <c r="B30" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>128562756</v>
       </c>
       <c r="B31" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>128556421</v>
       </c>
       <c r="B32" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>128829012</v>
       </c>
       <c r="B33" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>128827575</v>
       </c>
       <c r="B34" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>128822696</v>
       </c>
       <c r="B35" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>128828742</v>
       </c>
       <c r="B36" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>128827098</v>
       </c>
       <c r="B37" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>128830117</v>
       </c>
       <c r="B38" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>128827330</v>
       </c>
       <c r="B39" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>128828662</v>
       </c>
       <c r="B40" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>128827353</v>
       </c>
       <c r="B41" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>128568945</v>
       </c>
       <c r="B42" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>128563445</v>
       </c>
       <c r="B43" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>128828897</v>
       </c>
       <c r="B44" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>128563536</v>
       </c>
       <c r="B45" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>128828808</v>
       </c>
       <c r="B46" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>128827283</v>
       </c>
       <c r="B47" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6224,59 +6224,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128827411</v>
+        <v>128826691</v>
       </c>
       <c r="B48" t="n">
-        <v>98619</v>
+        <v>5177</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>542092</v>
+        <v>541964</v>
       </c>
       <c r="R48" t="n">
-        <v>6712255</v>
+        <v>6712107</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6308,7 +6294,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6318,12 +6304,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 14 ex på mindre yta.</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6350,45 +6331,59 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128826691</v>
+        <v>128827411</v>
       </c>
       <c r="B49" t="n">
-        <v>5177</v>
+        <v>98625</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541964</v>
+        <v>542092</v>
       </c>
       <c r="R49" t="n">
-        <v>6712107</v>
+        <v>6712255</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6420,7 +6415,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6430,7 +6425,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 14 ex på mindre yta.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6460,7 +6460,7 @@
         <v>128829197</v>
       </c>
       <c r="B50" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>128570551</v>
       </c>
       <c r="B51" t="n">
-        <v>86842</v>
+        <v>86846</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -1283,7 +1283,7 @@
         <v>128557953</v>
       </c>
       <c r="B7" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128569027</v>
       </c>
       <c r="B8" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>128557833</v>
       </c>
       <c r="B9" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128564663</v>
       </c>
       <c r="B10" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>128569151</v>
       </c>
       <c r="B11" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>128558408</v>
       </c>
       <c r="B12" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>128569182</v>
       </c>
       <c r="B13" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2232,60 +2232,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128558222</v>
+        <v>128568775</v>
       </c>
       <c r="B15" t="n">
-        <v>57876</v>
+        <v>98632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541897</v>
+        <v>542174</v>
       </c>
       <c r="R15" t="n">
-        <v>6712013</v>
+        <v>6712176</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2314,7 +2311,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2324,12 +2321,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Område där eventuellt en och samma individ flyger omkring</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2344,69 +2336,72 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Åsa Weinberg, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128568775</v>
+        <v>128558222</v>
       </c>
       <c r="B16" t="n">
-        <v>98625</v>
+        <v>57876</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>542174</v>
+        <v>541897</v>
       </c>
       <c r="R16" t="n">
-        <v>6712176</v>
+        <v>6712013</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2435,7 +2430,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2445,7 +2440,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Område där eventuellt en och samma individ flyger omkring</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2460,12 +2460,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Åsa Weinberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2590,7 +2590,7 @@
         <v>128557706</v>
       </c>
       <c r="B18" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>128567986</v>
       </c>
       <c r="B20" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>128569305</v>
       </c>
       <c r="B21" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>128568829</v>
       </c>
       <c r="B22" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>128569162</v>
       </c>
       <c r="B23" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>128568881</v>
       </c>
       <c r="B24" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>128563434</v>
       </c>
       <c r="B25" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>128557515</v>
       </c>
       <c r="B26" t="n">
-        <v>92817</v>
+        <v>92823</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3587,21 +3587,12 @@
       <c r="E26" t="n">
         <v>5449</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>5</t>
@@ -3817,7 +3808,7 @@
         <v>128569105</v>
       </c>
       <c r="B28" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3937,7 +3928,7 @@
         <v>128564481</v>
       </c>
       <c r="B29" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4063,10 +4054,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128827016</v>
+        <v>128562756</v>
       </c>
       <c r="B30" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4093,7 +4084,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4101,16 +4092,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>542101</v>
+        <v>542094</v>
       </c>
       <c r="R30" t="n">
-        <v>6712271</v>
+        <v>6712276</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4137,22 +4133,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 25 bladrosetter.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4172,17 +4173,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128562756</v>
+        <v>128827016</v>
       </c>
       <c r="B31" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4209,7 +4210,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4217,21 +4218,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>542094</v>
+        <v>542101</v>
       </c>
       <c r="R31" t="n">
-        <v>6712276</v>
+        <v>6712271</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4258,27 +4254,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Minst 25 bladrosetter.</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4298,7 +4289,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4308,7 +4299,7 @@
         <v>128556421</v>
       </c>
       <c r="B32" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4415,7 +4406,7 @@
         <v>128829012</v>
       </c>
       <c r="B33" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4541,7 +4532,7 @@
         <v>128827575</v>
       </c>
       <c r="B34" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4662,7 +4653,7 @@
         <v>128822696</v>
       </c>
       <c r="B35" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4774,7 +4765,7 @@
         <v>128828742</v>
       </c>
       <c r="B36" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4895,7 +4886,7 @@
         <v>128827098</v>
       </c>
       <c r="B37" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5021,7 +5012,7 @@
         <v>128830117</v>
       </c>
       <c r="B38" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5142,7 +5133,7 @@
         <v>128827330</v>
       </c>
       <c r="B39" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5268,7 +5259,7 @@
         <v>128828662</v>
       </c>
       <c r="B40" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5389,7 +5380,7 @@
         <v>128827353</v>
       </c>
       <c r="B41" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5510,7 +5501,7 @@
         <v>128568945</v>
       </c>
       <c r="B42" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5626,7 +5617,7 @@
         <v>128563445</v>
       </c>
       <c r="B43" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5752,7 +5743,7 @@
         <v>128828897</v>
       </c>
       <c r="B44" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5878,7 +5869,7 @@
         <v>128563536</v>
       </c>
       <c r="B45" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5985,7 +5976,7 @@
         <v>128828808</v>
       </c>
       <c r="B46" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6106,7 +6097,7 @@
         <v>128827283</v>
       </c>
       <c r="B47" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6334,7 +6325,7 @@
         <v>128827411</v>
       </c>
       <c r="B49" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6460,7 +6451,7 @@
         <v>128829197</v>
       </c>
       <c r="B50" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -1880,7 +1880,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128558408</v>
+        <v>128569182</v>
       </c>
       <c r="B12" t="n">
         <v>98632</v>
@@ -1923,21 +1923,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541940</v>
+        <v>542185</v>
       </c>
       <c r="R12" t="n">
-        <v>6712068</v>
+        <v>6712163</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1966,7 +1964,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1976,7 +1974,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1985,26 +1983,25 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Åsa Weinberg, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128569182</v>
+        <v>128558408</v>
       </c>
       <c r="B13" t="n">
         <v>98632</v>
@@ -2047,19 +2044,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>542185</v>
+        <v>541940</v>
       </c>
       <c r="R13" t="n">
-        <v>6712163</v>
+        <v>6712068</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2088,7 +2087,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2098,7 +2097,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2107,18 +2106,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Åsa Weinberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2232,57 +2232,60 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128568775</v>
+        <v>128558222</v>
       </c>
       <c r="B15" t="n">
-        <v>98632</v>
+        <v>57876</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542174</v>
+        <v>541897</v>
       </c>
       <c r="R15" t="n">
-        <v>6712176</v>
+        <v>6712013</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2311,7 +2314,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2321,7 +2324,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Område där eventuellt en och samma individ flyger omkring</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2336,72 +2344,69 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Åsa Weinberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128558222</v>
+        <v>128568775</v>
       </c>
       <c r="B16" t="n">
-        <v>57876</v>
+        <v>98632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541897</v>
+        <v>542174</v>
       </c>
       <c r="R16" t="n">
-        <v>6712013</v>
+        <v>6712176</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2430,7 +2435,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2440,12 +2445,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Område där eventuellt en och samma individ flyger omkring</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2460,12 +2460,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Åsa Weinberg, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2711,60 +2711,64 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128557356</v>
+        <v>128567986</v>
       </c>
       <c r="B19" t="n">
-        <v>57876</v>
+        <v>98632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541909</v>
+        <v>542207</v>
       </c>
       <c r="R19" t="n">
-        <v>6712025</v>
+        <v>6712193</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2793,7 +2797,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2803,7 +2807,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2812,6 +2816,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2830,64 +2835,60 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128567986</v>
+        <v>128557356</v>
       </c>
       <c r="B20" t="n">
-        <v>98632</v>
+        <v>57876</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>542207</v>
+        <v>541909</v>
       </c>
       <c r="R20" t="n">
-        <v>6712193</v>
+        <v>6712025</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2916,7 +2917,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2926,7 +2927,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2935,7 +2936,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3078,7 +3078,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128568829</v>
+        <v>128568723</v>
       </c>
       <c r="B22" t="n">
         <v>98632</v>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -5498,7 +5498,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128568945</v>
+        <v>128563445</v>
       </c>
       <c r="B42" t="n">
         <v>98632</v>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5536,16 +5536,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>542191</v>
+        <v>542085</v>
       </c>
       <c r="R42" t="n">
-        <v>6712170</v>
+        <v>6712250</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5577,7 +5582,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5587,7 +5592,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Minst femton friska bladrosetter.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5614,7 +5624,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128563445</v>
+        <v>128568945</v>
       </c>
       <c r="B43" t="n">
         <v>98632</v>
@@ -5644,7 +5654,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5652,21 +5662,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>542085</v>
+        <v>542191</v>
       </c>
       <c r="R43" t="n">
-        <v>6712250</v>
+        <v>6712170</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5698,7 +5703,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5708,12 +5713,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Minst femton friska bladrosetter.</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -4054,7 +4054,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128562756</v>
+        <v>128827016</v>
       </c>
       <c r="B30" t="n">
         <v>98632</v>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4092,21 +4092,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>542094</v>
+        <v>542101</v>
       </c>
       <c r="R30" t="n">
-        <v>6712276</v>
+        <v>6712271</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4133,27 +4128,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 25 bladrosetter.</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4173,14 +4163,14 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128827016</v>
+        <v>128562756</v>
       </c>
       <c r="B31" t="n">
         <v>98632</v>
@@ -4210,7 +4200,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4218,16 +4208,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>542101</v>
+        <v>542094</v>
       </c>
       <c r="R31" t="n">
-        <v>6712271</v>
+        <v>6712276</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4254,22 +4249,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Minst 25 bladrosetter.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -5498,7 +5498,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128563445</v>
+        <v>128568945</v>
       </c>
       <c r="B42" t="n">
         <v>98632</v>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5536,21 +5536,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>542085</v>
+        <v>542191</v>
       </c>
       <c r="R42" t="n">
-        <v>6712250</v>
+        <v>6712170</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5582,7 +5577,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5592,12 +5587,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Minst femton friska bladrosetter.</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5624,7 +5614,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128568945</v>
+        <v>128563445</v>
       </c>
       <c r="B43" t="n">
         <v>98632</v>
@@ -5654,7 +5644,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5662,16 +5652,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>542191</v>
+        <v>542085</v>
       </c>
       <c r="R43" t="n">
-        <v>6712170</v>
+        <v>6712250</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5703,7 +5698,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5713,7 +5708,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Minst femton friska bladrosetter.</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -1283,7 +1283,7 @@
         <v>128557953</v>
       </c>
       <c r="B7" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128569027</v>
       </c>
       <c r="B8" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>128557833</v>
       </c>
       <c r="B9" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128564663</v>
       </c>
       <c r="B10" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>128569151</v>
       </c>
       <c r="B11" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1880,10 +1880,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128569182</v>
+        <v>128558408</v>
       </c>
       <c r="B12" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,19 +1923,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>542185</v>
+        <v>541940</v>
       </c>
       <c r="R12" t="n">
-        <v>6712163</v>
+        <v>6712068</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1964,7 +1966,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1974,7 +1976,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1983,28 +1985,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Åsa Weinberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128558408</v>
+        <v>128569182</v>
       </c>
       <c r="B13" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2044,21 +2047,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541940</v>
+        <v>542185</v>
       </c>
       <c r="R13" t="n">
-        <v>6712068</v>
+        <v>6712163</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2087,7 +2088,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2097,7 +2098,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2106,19 +2107,18 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Åsa Weinberg, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2128,7 +2128,7 @@
         <v>128568250</v>
       </c>
       <c r="B14" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>128558222</v>
       </c>
       <c r="B15" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>128568775</v>
       </c>
       <c r="B16" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>128556581</v>
       </c>
       <c r="B17" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>128557706</v>
       </c>
       <c r="B18" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2711,64 +2711,60 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128567986</v>
+        <v>128557356</v>
       </c>
       <c r="B19" t="n">
-        <v>98632</v>
+        <v>57880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>542207</v>
+        <v>541909</v>
       </c>
       <c r="R19" t="n">
-        <v>6712193</v>
+        <v>6712025</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2797,7 +2793,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2807,7 +2803,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2816,7 +2812,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2835,60 +2830,64 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128557356</v>
+        <v>128567986</v>
       </c>
       <c r="B20" t="n">
-        <v>57876</v>
+        <v>98636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541909</v>
+        <v>542207</v>
       </c>
       <c r="R20" t="n">
-        <v>6712025</v>
+        <v>6712193</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2917,7 +2916,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2927,7 +2926,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2936,6 +2935,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>128569305</v>
       </c>
       <c r="B21" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3078,10 +3078,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128568723</v>
+        <v>128568829</v>
       </c>
       <c r="B22" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3205,7 +3205,7 @@
         <v>128569162</v>
       </c>
       <c r="B23" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>128568881</v>
       </c>
       <c r="B24" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>128563434</v>
       </c>
       <c r="B25" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>128557515</v>
       </c>
       <c r="B26" t="n">
-        <v>92823</v>
+        <v>92827</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>128561310</v>
       </c>
       <c r="B27" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>128569105</v>
       </c>
       <c r="B28" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>128564481</v>
       </c>
       <c r="B29" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4054,10 +4054,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128827016</v>
+        <v>128562756</v>
       </c>
       <c r="B30" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4092,16 +4092,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>542101</v>
+        <v>542094</v>
       </c>
       <c r="R30" t="n">
-        <v>6712271</v>
+        <v>6712276</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4128,22 +4133,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 25 bladrosetter.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4163,17 +4173,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128562756</v>
+        <v>128827016</v>
       </c>
       <c r="B31" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4200,7 +4210,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4208,21 +4218,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>542094</v>
+        <v>542101</v>
       </c>
       <c r="R31" t="n">
-        <v>6712276</v>
+        <v>6712271</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4249,27 +4254,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Minst 25 bladrosetter.</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4299,7 +4299,7 @@
         <v>128556421</v>
       </c>
       <c r="B32" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>128829012</v>
       </c>
       <c r="B33" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>128827575</v>
       </c>
       <c r="B34" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>128822696</v>
       </c>
       <c r="B35" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>128828742</v>
       </c>
       <c r="B36" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>128827098</v>
       </c>
       <c r="B37" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>128830117</v>
       </c>
       <c r="B38" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>128827330</v>
       </c>
       <c r="B39" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>128828662</v>
       </c>
       <c r="B40" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>128827353</v>
       </c>
       <c r="B41" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>128568945</v>
       </c>
       <c r="B42" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>128563445</v>
       </c>
       <c r="B43" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>128828897</v>
       </c>
       <c r="B44" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>128563536</v>
       </c>
       <c r="B45" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>128828808</v>
       </c>
       <c r="B46" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>128827283</v>
       </c>
       <c r="B47" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6215,45 +6215,59 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128826691</v>
+        <v>128827411</v>
       </c>
       <c r="B48" t="n">
-        <v>5177</v>
+        <v>98636</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541964</v>
+        <v>542092</v>
       </c>
       <c r="R48" t="n">
-        <v>6712107</v>
+        <v>6712255</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6285,7 +6299,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6295,7 +6309,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Minst 14 ex på mindre yta.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6322,59 +6341,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128827411</v>
+        <v>128826691</v>
       </c>
       <c r="B49" t="n">
-        <v>98632</v>
+        <v>5177</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>542092</v>
+        <v>541964</v>
       </c>
       <c r="R49" t="n">
-        <v>6712255</v>
+        <v>6712107</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6406,7 +6411,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6416,12 +6421,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Minst 14 ex på mindre yta.</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6451,7 +6451,7 @@
         <v>128829197</v>
       </c>
       <c r="B50" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>128570551</v>
       </c>
       <c r="B51" t="n">
-        <v>86846</v>
+        <v>86850</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4054,7 +4054,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128562756</v>
+        <v>128827016</v>
       </c>
       <c r="B30" t="n">
         <v>98636</v>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4092,21 +4092,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>542094</v>
+        <v>542101</v>
       </c>
       <c r="R30" t="n">
-        <v>6712276</v>
+        <v>6712271</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4133,27 +4128,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 25 bladrosetter.</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4173,14 +4163,14 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128827016</v>
+        <v>128556421</v>
       </c>
       <c r="B31" t="n">
         <v>98636</v>
@@ -4208,26 +4198,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>542101</v>
+        <v>541936</v>
       </c>
       <c r="R31" t="n">
-        <v>6712271</v>
+        <v>6711921</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4254,22 +4235,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4289,14 +4270,14 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128556421</v>
+        <v>128829012</v>
       </c>
       <c r="B32" t="n">
         <v>98636</v>
@@ -4324,17 +4305,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Torvströmyran, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541936</v>
+        <v>542184</v>
       </c>
       <c r="R32" t="n">
-        <v>6711921</v>
+        <v>6712198</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4361,22 +4356,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Minst 17 plantor på några dm 2.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4396,14 +4396,14 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128829012</v>
+        <v>128827575</v>
       </c>
       <c r="B33" t="n">
         <v>98636</v>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4441,21 +4441,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>542184</v>
+        <v>542092</v>
       </c>
       <c r="R33" t="n">
-        <v>6712198</v>
+        <v>6712254</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4487,7 +4482,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4497,12 +4492,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Minst 17 plantor på några dm 2.</t>
+          <t>Minst 30 plantor, varav 1 överblommade stängsel.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4529,7 +4524,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128827575</v>
+        <v>128822696</v>
       </c>
       <c r="B34" t="n">
         <v>98636</v>
@@ -4557,26 +4552,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>542092</v>
+        <v>542137</v>
       </c>
       <c r="R34" t="n">
-        <v>6712254</v>
+        <v>6712159</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4603,27 +4593,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:19</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Minst 30 plantor, varav 1 överblommade stängsel.</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4632,6 +4617,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4650,7 +4636,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128822696</v>
+        <v>128828742</v>
       </c>
       <c r="B35" t="n">
         <v>98636</v>
@@ -4678,21 +4664,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kroken, Falun, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>542137</v>
+        <v>542181</v>
       </c>
       <c r="R35" t="n">
-        <v>6712159</v>
+        <v>6712183</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4719,22 +4715,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4743,7 +4739,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4762,7 +4757,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128828742</v>
+        <v>128827098</v>
       </c>
       <c r="B36" t="n">
         <v>98636</v>
@@ -4792,7 +4787,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4802,7 +4797,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4811,10 +4806,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>542181</v>
+        <v>542101</v>
       </c>
       <c r="R36" t="n">
-        <v>6712183</v>
+        <v>6712275</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4846,7 +4841,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4856,7 +4851,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Cirka 50 plantor varav två överblommade stänglar, påyta om cirka 9,3x1,0 meter.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4883,7 +4883,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128827098</v>
+        <v>128830117</v>
       </c>
       <c r="B37" t="n">
         <v>98636</v>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4932,10 +4932,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>542101</v>
+        <v>542160</v>
       </c>
       <c r="R37" t="n">
-        <v>6712275</v>
+        <v>6712167</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4977,12 +4977,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Cirka 50 plantor varav två överblommade stänglar, påyta om cirka 9,3x1,0 meter.</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5009,7 +5004,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128830117</v>
+        <v>128827330</v>
       </c>
       <c r="B38" t="n">
         <v>98636</v>
@@ -5039,7 +5034,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5058,10 +5053,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>542160</v>
+        <v>542092</v>
       </c>
       <c r="R38" t="n">
-        <v>6712167</v>
+        <v>6712260</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5093,7 +5088,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5103,7 +5098,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 50 plantor som växer tätt på en yta om cirka 1x1 meter</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5130,7 +5130,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128827330</v>
+        <v>128828662</v>
       </c>
       <c r="B39" t="n">
         <v>98636</v>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>542092</v>
+        <v>542178</v>
       </c>
       <c r="R39" t="n">
-        <v>6712260</v>
+        <v>6712173</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5224,12 +5224,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Minst 50 plantor som växer tätt på en yta om cirka 1x1 meter</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5256,7 +5251,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128828662</v>
+        <v>128827353</v>
       </c>
       <c r="B40" t="n">
         <v>98636</v>
@@ -5286,7 +5281,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5305,10 +5300,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>542178</v>
+        <v>542091</v>
       </c>
       <c r="R40" t="n">
-        <v>6712173</v>
+        <v>6712256</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5340,7 +5335,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5350,7 +5345,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5377,7 +5372,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128827353</v>
+        <v>128568945</v>
       </c>
       <c r="B41" t="n">
         <v>98636</v>
@@ -5407,7 +5402,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5415,21 +5410,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>542091</v>
+        <v>542191</v>
       </c>
       <c r="R41" t="n">
-        <v>6712256</v>
+        <v>6712170</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5456,22 +5446,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5491,14 +5481,14 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128568945</v>
+        <v>128563445</v>
       </c>
       <c r="B42" t="n">
         <v>98636</v>
@@ -5528,7 +5518,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5536,16 +5526,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>542191</v>
+        <v>542085</v>
       </c>
       <c r="R42" t="n">
-        <v>6712170</v>
+        <v>6712250</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5577,7 +5572,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5587,7 +5582,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Minst femton friska bladrosetter.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5614,7 +5614,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128563445</v>
+        <v>128828897</v>
       </c>
       <c r="B43" t="n">
         <v>98636</v>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5663,10 +5663,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>542085</v>
+        <v>542192</v>
       </c>
       <c r="R43" t="n">
-        <v>6712250</v>
+        <v>6712176</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5693,27 +5693,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Minst femton friska bladrosetter.</t>
+          <t>Minst 30 ex på cirka 1 m2.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5733,14 +5733,14 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128828897</v>
+        <v>128828808</v>
       </c>
       <c r="B44" t="n">
         <v>98636</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5789,10 +5789,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>542192</v>
+        <v>542185</v>
       </c>
       <c r="R44" t="n">
-        <v>6712176</v>
+        <v>6712179</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5834,12 +5834,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:10</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minst 30 ex på cirka 1 m2.</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5866,7 +5861,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128563536</v>
+        <v>128827283</v>
       </c>
       <c r="B45" t="n">
         <v>98636</v>
@@ -5894,17 +5889,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>542088</v>
+        <v>542093</v>
       </c>
       <c r="R45" t="n">
-        <v>6712247</v>
+        <v>6712261</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5931,22 +5940,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5966,14 +5975,14 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128828808</v>
+        <v>128563536</v>
       </c>
       <c r="B46" t="n">
         <v>98636</v>
@@ -6001,31 +6010,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542185</v>
+        <v>542088</v>
       </c>
       <c r="R46" t="n">
-        <v>6712179</v>
+        <v>6712247</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6052,22 +6047,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6087,66 +6082,52 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128827283</v>
+        <v>128826691</v>
       </c>
       <c r="B47" t="n">
-        <v>98636</v>
+        <v>5177</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>542093</v>
+        <v>541964</v>
       </c>
       <c r="R47" t="n">
-        <v>6712261</v>
+        <v>6712107</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6178,7 +6159,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6188,7 +6169,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6341,45 +6322,59 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128826691</v>
+        <v>128829197</v>
       </c>
       <c r="B49" t="n">
-        <v>5177</v>
+        <v>98636</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541964</v>
+        <v>542186</v>
       </c>
       <c r="R49" t="n">
-        <v>6712107</v>
+        <v>6712207</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6411,7 +6406,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6421,7 +6416,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 56 plantor på cirka 0,5 m2.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6448,10 +6448,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128829197</v>
+        <v>128570551</v>
       </c>
       <c r="B50" t="n">
-        <v>98636</v>
+        <v>86850</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6459,51 +6459,48 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Torvströmyran, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>542186</v>
+        <v>542013</v>
       </c>
       <c r="R50" t="n">
-        <v>6712207</v>
+        <v>6712124</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6527,27 +6524,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Minst 56 plantor på cirka 0,5 m2.</t>
+          <t>Jan-Olof Hermansson har utifrån fotona bekräftat arten.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6556,6 +6553,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6567,134 +6565,10 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>128570551</v>
-      </c>
-      <c r="B51" t="n">
-        <v>86850</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>442</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Bullspindling</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Cortinarius corrosus</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Torvströmyran, Kroken, Dlr</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>542013</v>
-      </c>
-      <c r="R51" t="n">
-        <v>6712124</v>
-      </c>
-      <c r="S51" t="n">
-        <v>25</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Vika</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Jan-Olof Hermansson har utifrån fotona bekräftat arten.</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -2232,60 +2232,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128558222</v>
+        <v>128568775</v>
       </c>
       <c r="B15" t="n">
-        <v>57880</v>
+        <v>98636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541897</v>
+        <v>542174</v>
       </c>
       <c r="R15" t="n">
-        <v>6712013</v>
+        <v>6712176</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2314,7 +2311,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2324,12 +2321,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Område där eventuellt en och samma individ flyger omkring</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2344,69 +2336,72 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Åsa Weinberg, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128568775</v>
+        <v>128558222</v>
       </c>
       <c r="B16" t="n">
-        <v>98636</v>
+        <v>57880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>542174</v>
+        <v>541897</v>
       </c>
       <c r="R16" t="n">
-        <v>6712176</v>
+        <v>6712013</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2435,7 +2430,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2445,7 +2440,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Område där eventuellt en och samma individ flyger omkring</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2460,12 +2460,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Åsa Weinberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -5740,7 +5740,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128828808</v>
+        <v>128563536</v>
       </c>
       <c r="B44" t="n">
         <v>98636</v>
@@ -5768,31 +5768,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>542185</v>
+        <v>542088</v>
       </c>
       <c r="R44" t="n">
-        <v>6712179</v>
+        <v>6712247</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5819,22 +5805,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5854,7 +5840,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5982,7 +5968,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128563536</v>
+        <v>128828808</v>
       </c>
       <c r="B46" t="n">
         <v>98636</v>
@@ -6010,17 +5996,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542088</v>
+        <v>542185</v>
       </c>
       <c r="R46" t="n">
-        <v>6712247</v>
+        <v>6712179</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6047,22 +6047,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6082,52 +6082,66 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128826691</v>
+        <v>128827411</v>
       </c>
       <c r="B47" t="n">
-        <v>5177</v>
+        <v>98636</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541964</v>
+        <v>542092</v>
       </c>
       <c r="R47" t="n">
-        <v>6712107</v>
+        <v>6712255</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6159,7 +6173,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6169,7 +6183,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Minst 14 ex på mindre yta.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6196,59 +6215,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128827411</v>
+        <v>128826691</v>
       </c>
       <c r="B48" t="n">
-        <v>98636</v>
+        <v>5177</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>542092</v>
+        <v>541964</v>
       </c>
       <c r="R48" t="n">
-        <v>6712255</v>
+        <v>6712107</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6280,7 +6285,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6290,12 +6295,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 14 ex på mindre yta.</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -1283,7 +1283,7 @@
         <v>128557953</v>
       </c>
       <c r="B7" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128569027</v>
       </c>
       <c r="B8" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>128557833</v>
       </c>
       <c r="B9" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128564663</v>
       </c>
       <c r="B10" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>128569151</v>
       </c>
       <c r="B11" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>128558408</v>
       </c>
       <c r="B12" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>128569182</v>
       </c>
       <c r="B13" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>128568250</v>
       </c>
       <c r="B14" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2232,57 +2232,60 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128568775</v>
+        <v>128558222</v>
       </c>
       <c r="B15" t="n">
-        <v>98636</v>
+        <v>57883</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542174</v>
+        <v>541897</v>
       </c>
       <c r="R15" t="n">
-        <v>6712176</v>
+        <v>6712013</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2311,7 +2314,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2321,7 +2324,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Område där eventuellt en och samma individ flyger omkring</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2336,72 +2344,69 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Åsa Weinberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128558222</v>
+        <v>128568775</v>
       </c>
       <c r="B16" t="n">
-        <v>57880</v>
+        <v>98643</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541897</v>
+        <v>542174</v>
       </c>
       <c r="R16" t="n">
-        <v>6712013</v>
+        <v>6712176</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2430,7 +2435,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2440,12 +2445,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Område där eventuellt en och samma individ flyger omkring</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2460,12 +2460,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Åsa Weinberg, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
         <v>128556581</v>
       </c>
       <c r="B17" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>128557706</v>
       </c>
       <c r="B18" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>128557356</v>
       </c>
       <c r="B19" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>128567986</v>
       </c>
       <c r="B20" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>128569305</v>
       </c>
       <c r="B21" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>128568829</v>
       </c>
       <c r="B22" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>128569162</v>
       </c>
       <c r="B23" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>128568881</v>
       </c>
       <c r="B24" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>128563434</v>
       </c>
       <c r="B25" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>128557515</v>
       </c>
       <c r="B26" t="n">
-        <v>92827</v>
+        <v>92832</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3686,60 +3686,60 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128561310</v>
+        <v>128569105</v>
       </c>
       <c r="B27" t="n">
-        <v>57880</v>
+        <v>98643</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541975</v>
+        <v>542192</v>
       </c>
       <c r="R27" t="n">
-        <v>6712087</v>
+        <v>6712166</v>
       </c>
       <c r="S27" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3787,6 +3787,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3805,60 +3806,60 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128569105</v>
+        <v>128561310</v>
       </c>
       <c r="B28" t="n">
-        <v>98636</v>
+        <v>57883</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542192</v>
+        <v>541975</v>
       </c>
       <c r="R28" t="n">
-        <v>6712166</v>
+        <v>6712087</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3887,7 +3888,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3897,7 +3898,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3906,7 +3907,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3928,7 +3928,7 @@
         <v>128564481</v>
       </c>
       <c r="B29" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>128827016</v>
       </c>
       <c r="B30" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>128556421</v>
       </c>
       <c r="B31" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>128829012</v>
       </c>
       <c r="B32" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>128827575</v>
       </c>
       <c r="B33" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>128822696</v>
       </c>
       <c r="B34" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>128828742</v>
       </c>
       <c r="B35" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>128827098</v>
       </c>
       <c r="B36" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>128830117</v>
       </c>
       <c r="B37" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>128827330</v>
       </c>
       <c r="B38" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5130,10 +5130,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128828662</v>
+        <v>128827353</v>
       </c>
       <c r="B39" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>542178</v>
+        <v>542091</v>
       </c>
       <c r="R39" t="n">
-        <v>6712173</v>
+        <v>6712256</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5251,10 +5251,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128827353</v>
+        <v>128828662</v>
       </c>
       <c r="B40" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5300,10 +5300,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>542091</v>
+        <v>542178</v>
       </c>
       <c r="R40" t="n">
-        <v>6712256</v>
+        <v>6712173</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5375,7 +5375,7 @@
         <v>128568945</v>
       </c>
       <c r="B41" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>128563445</v>
       </c>
       <c r="B42" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>128828897</v>
       </c>
       <c r="B43" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>128563536</v>
       </c>
       <c r="B44" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5847,10 +5847,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128827283</v>
+        <v>128828808</v>
       </c>
       <c r="B45" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5892,14 +5892,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>542093</v>
+        <v>542185</v>
       </c>
       <c r="R45" t="n">
-        <v>6712261</v>
+        <v>6712179</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5968,10 +5968,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128828808</v>
+        <v>128827283</v>
       </c>
       <c r="B46" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6013,14 +6013,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542185</v>
+        <v>542093</v>
       </c>
       <c r="R46" t="n">
-        <v>6712179</v>
+        <v>6712261</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6089,59 +6089,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128827411</v>
+        <v>128826691</v>
       </c>
       <c r="B47" t="n">
-        <v>98636</v>
+        <v>5177</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>542092</v>
+        <v>541964</v>
       </c>
       <c r="R47" t="n">
-        <v>6712255</v>
+        <v>6712107</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6173,7 +6159,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6183,12 +6169,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Minst 14 ex på mindre yta.</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6215,45 +6196,59 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128826691</v>
+        <v>128827411</v>
       </c>
       <c r="B48" t="n">
-        <v>5177</v>
+        <v>98643</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541964</v>
+        <v>542092</v>
       </c>
       <c r="R48" t="n">
-        <v>6712107</v>
+        <v>6712255</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6285,7 +6280,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6295,7 +6290,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Minst 14 ex på mindre yta.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6325,7 +6325,7 @@
         <v>128829197</v>
       </c>
       <c r="B49" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>128570551</v>
       </c>
       <c r="B50" t="n">
-        <v>86850</v>
+        <v>86855</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -1283,7 +1283,7 @@
         <v>128557953</v>
       </c>
       <c r="B7" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128569027</v>
       </c>
       <c r="B8" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>128557833</v>
       </c>
       <c r="B9" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128564663</v>
       </c>
       <c r="B10" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>128569151</v>
       </c>
       <c r="B11" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1880,10 +1880,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128558408</v>
+        <v>128569182</v>
       </c>
       <c r="B12" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,21 +1923,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541940</v>
+        <v>542185</v>
       </c>
       <c r="R12" t="n">
-        <v>6712068</v>
+        <v>6712163</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1966,7 +1964,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1976,7 +1974,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1985,29 +1983,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Åsa Weinberg, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128569182</v>
+        <v>128558408</v>
       </c>
       <c r="B13" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,19 +2044,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>542185</v>
+        <v>541940</v>
       </c>
       <c r="R13" t="n">
-        <v>6712163</v>
+        <v>6712068</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2088,7 +2087,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2098,7 +2097,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2107,18 +2106,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Åsa Weinberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2128,7 +2128,7 @@
         <v>128568250</v>
       </c>
       <c r="B14" t="n">
-        <v>83005</v>
+        <v>83010</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>128568775</v>
       </c>
       <c r="B15" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>128557706</v>
       </c>
       <c r="B18" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>128567986</v>
       </c>
       <c r="B20" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>128569305</v>
       </c>
       <c r="B21" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3078,10 +3078,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128568829</v>
+        <v>128568723</v>
       </c>
       <c r="B22" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3205,7 +3205,7 @@
         <v>128569162</v>
       </c>
       <c r="B23" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>128568881</v>
       </c>
       <c r="B24" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>128563434</v>
       </c>
       <c r="B25" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>128557515</v>
       </c>
       <c r="B26" t="n">
-        <v>92835</v>
+        <v>92840</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>128569105</v>
       </c>
       <c r="B27" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>128564481</v>
       </c>
       <c r="B29" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128828808</v>
+        <v>128563536</v>
       </c>
       <c r="B44" t="n">
         <v>98651</v>
@@ -5768,31 +5768,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>542185</v>
+        <v>542088</v>
       </c>
       <c r="R44" t="n">
-        <v>6712179</v>
+        <v>6712247</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5819,22 +5805,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5854,14 +5840,14 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128827283</v>
+        <v>128828808</v>
       </c>
       <c r="B45" t="n">
         <v>98651</v>
@@ -5891,7 +5877,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5906,14 +5892,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>542093</v>
+        <v>542185</v>
       </c>
       <c r="R45" t="n">
-        <v>6712261</v>
+        <v>6712179</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5945,7 +5931,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5955,7 +5941,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5982,7 +5968,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128563536</v>
+        <v>128827283</v>
       </c>
       <c r="B46" t="n">
         <v>98651</v>
@@ -6010,17 +5996,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542088</v>
+        <v>542093</v>
       </c>
       <c r="R46" t="n">
-        <v>6712247</v>
+        <v>6712261</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6047,22 +6047,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -1880,7 +1880,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128569182</v>
+        <v>128558408</v>
       </c>
       <c r="B12" t="n">
         <v>98651</v>
@@ -1923,19 +1923,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>542185</v>
+        <v>541940</v>
       </c>
       <c r="R12" t="n">
-        <v>6712163</v>
+        <v>6712068</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1964,7 +1966,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1974,7 +1976,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1983,25 +1985,26 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Åsa Weinberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128558408</v>
+        <v>128569182</v>
       </c>
       <c r="B13" t="n">
         <v>98651</v>
@@ -2044,21 +2047,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541940</v>
+        <v>542185</v>
       </c>
       <c r="R13" t="n">
-        <v>6712068</v>
+        <v>6712163</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2087,7 +2088,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2097,7 +2098,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2106,19 +2107,18 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Åsa Weinberg, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2232,57 +2232,60 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128568775</v>
+        <v>128558222</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>57883</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542174</v>
+        <v>541897</v>
       </c>
       <c r="R15" t="n">
-        <v>6712176</v>
+        <v>6712013</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2311,7 +2314,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2321,7 +2324,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Område där eventuellt en och samma individ flyger omkring</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2336,72 +2344,69 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Åsa Weinberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128558222</v>
+        <v>128568775</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
+        <v>98651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541897</v>
+        <v>542174</v>
       </c>
       <c r="R16" t="n">
-        <v>6712013</v>
+        <v>6712176</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2430,7 +2435,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2440,12 +2445,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Område där eventuellt en och samma individ flyger omkring</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2460,12 +2460,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Åsa Weinberg, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -3078,7 +3078,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128568723</v>
+        <v>128568829</v>
       </c>
       <c r="B22" t="n">
         <v>98651</v>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3686,60 +3686,60 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128569105</v>
+        <v>128561310</v>
       </c>
       <c r="B27" t="n">
-        <v>98651</v>
+        <v>57883</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>542192</v>
+        <v>541975</v>
       </c>
       <c r="R27" t="n">
-        <v>6712166</v>
+        <v>6712087</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3787,7 +3787,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3806,60 +3805,60 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128561310</v>
+        <v>128569105</v>
       </c>
       <c r="B28" t="n">
-        <v>57883</v>
+        <v>98651</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541975</v>
+        <v>542192</v>
       </c>
       <c r="R28" t="n">
-        <v>6712087</v>
+        <v>6712166</v>
       </c>
       <c r="S28" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3888,7 +3887,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3898,7 +3897,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3907,6 +3906,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4057,7 +4057,7 @@
         <v>128827016</v>
       </c>
       <c r="B30" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>128556421</v>
       </c>
       <c r="B31" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>128829012</v>
       </c>
       <c r="B32" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>128827575</v>
       </c>
       <c r="B33" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>128822696</v>
       </c>
       <c r="B34" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>128828742</v>
       </c>
       <c r="B35" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>128827098</v>
       </c>
       <c r="B36" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>128830117</v>
       </c>
       <c r="B37" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>128827330</v>
       </c>
       <c r="B38" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>128828662</v>
       </c>
       <c r="B39" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>128827353</v>
       </c>
       <c r="B40" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>128563445</v>
       </c>
       <c r="B41" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>128568945</v>
       </c>
       <c r="B42" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>128828897</v>
       </c>
       <c r="B43" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>128563536</v>
       </c>
       <c r="B44" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>128828808</v>
       </c>
       <c r="B45" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>128827283</v>
       </c>
       <c r="B46" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6089,45 +6089,59 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128826691</v>
+        <v>128827411</v>
       </c>
       <c r="B47" t="n">
-        <v>5177</v>
+        <v>98656</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541964</v>
+        <v>542092</v>
       </c>
       <c r="R47" t="n">
-        <v>6712107</v>
+        <v>6712255</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6159,7 +6173,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6169,7 +6183,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Minst 14 ex på mindre yta.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6196,59 +6215,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128827411</v>
+        <v>128826691</v>
       </c>
       <c r="B48" t="n">
-        <v>98651</v>
+        <v>5177</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>542092</v>
+        <v>541964</v>
       </c>
       <c r="R48" t="n">
-        <v>6712255</v>
+        <v>6712107</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6280,7 +6285,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6290,12 +6295,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 14 ex på mindre yta.</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6325,7 +6325,7 @@
         <v>128829197</v>
       </c>
       <c r="B49" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>128570551</v>
       </c>
       <c r="B50" t="n">
-        <v>86862</v>
+        <v>86865</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -1283,7 +1283,7 @@
         <v>128557953</v>
       </c>
       <c r="B7" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128569027</v>
       </c>
       <c r="B8" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>128557833</v>
       </c>
       <c r="B9" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128564663</v>
       </c>
       <c r="B10" t="n">
-        <v>92823</v>
+        <v>92831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>128569151</v>
       </c>
       <c r="B11" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1880,10 +1880,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128558408</v>
+        <v>128569182</v>
       </c>
       <c r="B12" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,21 +1923,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541940</v>
+        <v>542185</v>
       </c>
       <c r="R12" t="n">
-        <v>6712068</v>
+        <v>6712163</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1966,7 +1964,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1976,7 +1974,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1985,29 +1983,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Åsa Weinberg, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128569182</v>
+        <v>128558408</v>
       </c>
       <c r="B13" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,19 +2044,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>542185</v>
+        <v>541940</v>
       </c>
       <c r="R13" t="n">
-        <v>6712163</v>
+        <v>6712068</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2088,7 +2087,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2098,7 +2097,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2107,18 +2106,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Åsa Weinberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Åsa Weinberg, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2128,7 +2128,7 @@
         <v>128568250</v>
       </c>
       <c r="B14" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>128568775</v>
       </c>
       <c r="B16" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>128557706</v>
       </c>
       <c r="B18" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2711,60 +2711,64 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128557356</v>
+        <v>128567986</v>
       </c>
       <c r="B19" t="n">
-        <v>57883</v>
+        <v>98659</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541909</v>
+        <v>542207</v>
       </c>
       <c r="R19" t="n">
-        <v>6712025</v>
+        <v>6712193</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2793,7 +2797,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2803,7 +2807,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2812,6 +2816,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2830,64 +2835,60 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128567986</v>
+        <v>128557356</v>
       </c>
       <c r="B20" t="n">
-        <v>98651</v>
+        <v>57883</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>542207</v>
+        <v>541909</v>
       </c>
       <c r="R20" t="n">
-        <v>6712193</v>
+        <v>6712025</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2916,7 +2917,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2926,7 +2927,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2935,7 +2936,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>128569305</v>
       </c>
       <c r="B21" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3078,10 +3078,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128568829</v>
+        <v>128568723</v>
       </c>
       <c r="B22" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3205,7 +3205,7 @@
         <v>128569162</v>
       </c>
       <c r="B23" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>128568881</v>
       </c>
       <c r="B24" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>128563434</v>
       </c>
       <c r="B25" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>128557515</v>
       </c>
       <c r="B26" t="n">
-        <v>92840</v>
+        <v>92848</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3686,60 +3686,60 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128561310</v>
+        <v>128569105</v>
       </c>
       <c r="B27" t="n">
-        <v>57883</v>
+        <v>98659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541975</v>
+        <v>542192</v>
       </c>
       <c r="R27" t="n">
-        <v>6712087</v>
+        <v>6712166</v>
       </c>
       <c r="S27" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3787,6 +3787,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3805,60 +3806,60 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128569105</v>
+        <v>128561310</v>
       </c>
       <c r="B28" t="n">
-        <v>98651</v>
+        <v>57883</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542192</v>
+        <v>541975</v>
       </c>
       <c r="R28" t="n">
-        <v>6712166</v>
+        <v>6712087</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3887,7 +3888,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3897,7 +3898,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3906,7 +3907,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3928,7 +3928,7 @@
         <v>128564481</v>
       </c>
       <c r="B29" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>128827016</v>
       </c>
       <c r="B30" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>128556421</v>
       </c>
       <c r="B31" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>128829012</v>
       </c>
       <c r="B32" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>128827575</v>
       </c>
       <c r="B33" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>128822696</v>
       </c>
       <c r="B34" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>128828742</v>
       </c>
       <c r="B35" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>128827098</v>
       </c>
       <c r="B36" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>128830117</v>
       </c>
       <c r="B37" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>128827330</v>
       </c>
       <c r="B38" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>128828662</v>
       </c>
       <c r="B39" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>128827353</v>
       </c>
       <c r="B40" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>128563445</v>
       </c>
       <c r="B41" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>128568945</v>
       </c>
       <c r="B42" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>128828897</v>
       </c>
       <c r="B43" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5740,10 +5740,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128563536</v>
+        <v>128828808</v>
       </c>
       <c r="B44" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5768,17 +5768,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>542088</v>
+        <v>542185</v>
       </c>
       <c r="R44" t="n">
-        <v>6712247</v>
+        <v>6712179</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5805,22 +5819,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5840,17 +5854,17 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128828808</v>
+        <v>128827283</v>
       </c>
       <c r="B45" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5877,7 +5891,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5892,14 +5906,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>542185</v>
+        <v>542093</v>
       </c>
       <c r="R45" t="n">
-        <v>6712179</v>
+        <v>6712261</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5931,7 +5945,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5941,7 +5955,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5968,10 +5982,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128827283</v>
+        <v>128563536</v>
       </c>
       <c r="B46" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5996,31 +6010,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542093</v>
+        <v>542088</v>
       </c>
       <c r="R46" t="n">
-        <v>6712261</v>
+        <v>6712247</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6047,22 +6047,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6092,7 +6092,7 @@
         <v>128827411</v>
       </c>
       <c r="B47" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>128829197</v>
       </c>
       <c r="B49" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>128570551</v>
       </c>
       <c r="B50" t="n">
-        <v>86865</v>
+        <v>86868</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -5130,7 +5130,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128828662</v>
+        <v>128827353</v>
       </c>
       <c r="B39" t="n">
         <v>98659</v>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>542178</v>
+        <v>542091</v>
       </c>
       <c r="R39" t="n">
-        <v>6712173</v>
+        <v>6712256</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5251,7 +5251,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128827353</v>
+        <v>128828662</v>
       </c>
       <c r="B40" t="n">
         <v>98659</v>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5300,10 +5300,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>542091</v>
+        <v>542178</v>
       </c>
       <c r="R40" t="n">
-        <v>6712256</v>
+        <v>6712173</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5372,7 +5372,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128563445</v>
+        <v>128568945</v>
       </c>
       <c r="B41" t="n">
         <v>98659</v>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5410,21 +5410,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>542085</v>
+        <v>542191</v>
       </c>
       <c r="R41" t="n">
-        <v>6712250</v>
+        <v>6712170</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5456,7 +5451,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5466,12 +5461,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Minst femton friska bladrosetter.</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5498,7 +5488,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128568945</v>
+        <v>128563445</v>
       </c>
       <c r="B42" t="n">
         <v>98659</v>
@@ -5528,7 +5518,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5536,16 +5526,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>542191</v>
+        <v>542085</v>
       </c>
       <c r="R42" t="n">
-        <v>6712170</v>
+        <v>6712250</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5577,7 +5572,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5587,7 +5582,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Minst femton friska bladrosetter.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5740,7 +5740,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128828808</v>
+        <v>128563536</v>
       </c>
       <c r="B44" t="n">
         <v>98659</v>
@@ -5768,31 +5768,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>542185</v>
+        <v>542088</v>
       </c>
       <c r="R44" t="n">
-        <v>6712179</v>
+        <v>6712247</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5819,22 +5805,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5854,14 +5840,14 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128827283</v>
+        <v>128828808</v>
       </c>
       <c r="B45" t="n">
         <v>98659</v>
@@ -5891,7 +5877,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5906,14 +5892,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>542093</v>
+        <v>542185</v>
       </c>
       <c r="R45" t="n">
-        <v>6712261</v>
+        <v>6712179</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5945,7 +5931,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5955,7 +5941,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5982,7 +5968,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128563536</v>
+        <v>128827283</v>
       </c>
       <c r="B46" t="n">
         <v>98659</v>
@@ -6010,17 +5996,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542088</v>
+        <v>542093</v>
       </c>
       <c r="R46" t="n">
-        <v>6712247</v>
+        <v>6712261</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6047,22 +6047,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6082,66 +6082,52 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128827411</v>
+        <v>128826691</v>
       </c>
       <c r="B47" t="n">
-        <v>98659</v>
+        <v>5177</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>542092</v>
+        <v>541964</v>
       </c>
       <c r="R47" t="n">
-        <v>6712255</v>
+        <v>6712107</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6173,7 +6159,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6183,12 +6169,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Minst 14 ex på mindre yta.</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6215,45 +6196,59 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128826691</v>
+        <v>128827411</v>
       </c>
       <c r="B48" t="n">
-        <v>5177</v>
+        <v>98659</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541964</v>
+        <v>542092</v>
       </c>
       <c r="R48" t="n">
-        <v>6712107</v>
+        <v>6712255</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6285,7 +6280,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6295,7 +6290,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Minst 14 ex på mindre yta.</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -3078,7 +3078,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128568723</v>
+        <v>128568829</v>
       </c>
       <c r="B22" t="n">
         <v>98659</v>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3686,60 +3686,60 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128569105</v>
+        <v>128561310</v>
       </c>
       <c r="B27" t="n">
-        <v>98659</v>
+        <v>57883</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>542192</v>
+        <v>541975</v>
       </c>
       <c r="R27" t="n">
-        <v>6712166</v>
+        <v>6712087</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3787,7 +3787,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3806,60 +3805,60 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128561310</v>
+        <v>128569105</v>
       </c>
       <c r="B28" t="n">
-        <v>57883</v>
+        <v>98659</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541975</v>
+        <v>542192</v>
       </c>
       <c r="R28" t="n">
-        <v>6712087</v>
+        <v>6712166</v>
       </c>
       <c r="S28" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3888,7 +3887,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3898,7 +3897,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3907,6 +3906,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -5740,7 +5740,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128563536</v>
+        <v>128828808</v>
       </c>
       <c r="B44" t="n">
         <v>98659</v>
@@ -5768,17 +5768,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>542088</v>
+        <v>542185</v>
       </c>
       <c r="R44" t="n">
-        <v>6712247</v>
+        <v>6712179</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5805,22 +5819,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5840,14 +5854,14 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128828808</v>
+        <v>128827283</v>
       </c>
       <c r="B45" t="n">
         <v>98659</v>
@@ -5877,7 +5891,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5892,14 +5906,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>542185</v>
+        <v>542093</v>
       </c>
       <c r="R45" t="n">
-        <v>6712179</v>
+        <v>6712261</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5931,7 +5945,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5941,7 +5955,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5968,7 +5982,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128827283</v>
+        <v>128563536</v>
       </c>
       <c r="B46" t="n">
         <v>98659</v>
@@ -5996,31 +6010,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542093</v>
+        <v>542088</v>
       </c>
       <c r="R46" t="n">
-        <v>6712261</v>
+        <v>6712247</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6047,22 +6047,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6082,52 +6082,66 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128826691</v>
+        <v>128827411</v>
       </c>
       <c r="B47" t="n">
-        <v>5177</v>
+        <v>98659</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541964</v>
+        <v>542092</v>
       </c>
       <c r="R47" t="n">
-        <v>6712107</v>
+        <v>6712255</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6159,7 +6173,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6169,7 +6183,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Minst 14 ex på mindre yta.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6196,59 +6215,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128827411</v>
+        <v>128826691</v>
       </c>
       <c r="B48" t="n">
-        <v>98659</v>
+        <v>5177</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>542092</v>
+        <v>541964</v>
       </c>
       <c r="R48" t="n">
-        <v>6712255</v>
+        <v>6712107</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6280,7 +6285,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6290,12 +6295,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 14 ex på mindre yta.</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -5130,7 +5130,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128827353</v>
+        <v>128828662</v>
       </c>
       <c r="B39" t="n">
         <v>98659</v>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>542091</v>
+        <v>542178</v>
       </c>
       <c r="R39" t="n">
-        <v>6712256</v>
+        <v>6712173</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5251,7 +5251,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128828662</v>
+        <v>128827353</v>
       </c>
       <c r="B40" t="n">
         <v>98659</v>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5300,10 +5300,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>542178</v>
+        <v>542091</v>
       </c>
       <c r="R40" t="n">
-        <v>6712173</v>
+        <v>6712256</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5372,7 +5372,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128568945</v>
+        <v>128563445</v>
       </c>
       <c r="B41" t="n">
         <v>98659</v>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5410,16 +5410,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>542191</v>
+        <v>542085</v>
       </c>
       <c r="R41" t="n">
-        <v>6712170</v>
+        <v>6712250</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5451,7 +5456,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5461,7 +5466,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Minst femton friska bladrosetter.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5488,7 +5498,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128563445</v>
+        <v>128568945</v>
       </c>
       <c r="B42" t="n">
         <v>98659</v>
@@ -5518,7 +5528,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5526,21 +5536,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>542085</v>
+        <v>542191</v>
       </c>
       <c r="R42" t="n">
-        <v>6712250</v>
+        <v>6712170</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5572,7 +5577,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5582,12 +5587,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Minst femton friska bladrosetter.</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5740,7 +5740,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128828808</v>
+        <v>128563536</v>
       </c>
       <c r="B44" t="n">
         <v>98659</v>
@@ -5768,31 +5768,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>542185</v>
+        <v>542088</v>
       </c>
       <c r="R44" t="n">
-        <v>6712179</v>
+        <v>6712247</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5819,22 +5805,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5854,14 +5840,14 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128827283</v>
+        <v>128828808</v>
       </c>
       <c r="B45" t="n">
         <v>98659</v>
@@ -5891,7 +5877,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5906,14 +5892,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>542093</v>
+        <v>542185</v>
       </c>
       <c r="R45" t="n">
-        <v>6712261</v>
+        <v>6712179</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5945,7 +5931,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5955,7 +5941,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5982,7 +5968,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128563536</v>
+        <v>128827283</v>
       </c>
       <c r="B46" t="n">
         <v>98659</v>
@@ -6010,17 +5996,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542088</v>
+        <v>542093</v>
       </c>
       <c r="R46" t="n">
-        <v>6712247</v>
+        <v>6712261</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6047,22 +6047,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6082,66 +6082,52 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128827411</v>
+        <v>128826691</v>
       </c>
       <c r="B47" t="n">
-        <v>98659</v>
+        <v>5177</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>542092</v>
+        <v>541964</v>
       </c>
       <c r="R47" t="n">
-        <v>6712255</v>
+        <v>6712107</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6173,7 +6159,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6183,12 +6169,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Minst 14 ex på mindre yta.</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6215,45 +6196,59 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128826691</v>
+        <v>128827411</v>
       </c>
       <c r="B48" t="n">
-        <v>5177</v>
+        <v>98659</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541964</v>
+        <v>542092</v>
       </c>
       <c r="R48" t="n">
-        <v>6712107</v>
+        <v>6712255</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6285,7 +6280,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6295,7 +6290,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Minst 14 ex på mindre yta.</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -4057,7 +4057,7 @@
         <v>128827016</v>
       </c>
       <c r="B30" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>128556421</v>
       </c>
       <c r="B31" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>128829012</v>
       </c>
       <c r="B32" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>128827575</v>
       </c>
       <c r="B33" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>128822696</v>
       </c>
       <c r="B34" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>128828742</v>
       </c>
       <c r="B35" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>128827098</v>
       </c>
       <c r="B36" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>128830117</v>
       </c>
       <c r="B37" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>128827330</v>
       </c>
       <c r="B38" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>128828662</v>
       </c>
       <c r="B39" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>128827353</v>
       </c>
       <c r="B40" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5372,10 +5372,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128563445</v>
+        <v>128568945</v>
       </c>
       <c r="B41" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5410,21 +5410,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>542085</v>
+        <v>542191</v>
       </c>
       <c r="R41" t="n">
-        <v>6712250</v>
+        <v>6712170</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5456,7 +5451,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5466,12 +5461,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Minst femton friska bladrosetter.</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5498,10 +5488,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128568945</v>
+        <v>128563445</v>
       </c>
       <c r="B42" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5528,7 +5518,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5536,16 +5526,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>542191</v>
+        <v>542085</v>
       </c>
       <c r="R42" t="n">
-        <v>6712170</v>
+        <v>6712250</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5577,7 +5572,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5587,7 +5582,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Minst femton friska bladrosetter.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5617,7 +5617,7 @@
         <v>128828897</v>
       </c>
       <c r="B43" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>128563536</v>
       </c>
       <c r="B44" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>128828808</v>
       </c>
       <c r="B45" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>128827283</v>
       </c>
       <c r="B46" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>128827411</v>
       </c>
       <c r="B48" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>128829197</v>
       </c>
       <c r="B49" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>128570551</v>
       </c>
       <c r="B50" t="n">
-        <v>86868</v>
+        <v>86872</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -4057,7 +4057,7 @@
         <v>128827016</v>
       </c>
       <c r="B30" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>128556421</v>
       </c>
       <c r="B31" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>128829012</v>
       </c>
       <c r="B32" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>128827575</v>
       </c>
       <c r="B33" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>128822696</v>
       </c>
       <c r="B34" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>128828742</v>
       </c>
       <c r="B35" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>128827098</v>
       </c>
       <c r="B36" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>128830117</v>
       </c>
       <c r="B37" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>128827330</v>
       </c>
       <c r="B38" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>128828662</v>
       </c>
       <c r="B39" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>128827353</v>
       </c>
       <c r="B40" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>128568945</v>
       </c>
       <c r="B41" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>128563445</v>
       </c>
       <c r="B42" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>128828897</v>
       </c>
       <c r="B43" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>128563536</v>
       </c>
       <c r="B44" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>128828808</v>
       </c>
       <c r="B45" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>128827283</v>
       </c>
       <c r="B46" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6089,45 +6089,59 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128826691</v>
+        <v>128827411</v>
       </c>
       <c r="B47" t="n">
-        <v>5177</v>
+        <v>98676</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541964</v>
+        <v>542092</v>
       </c>
       <c r="R47" t="n">
-        <v>6712107</v>
+        <v>6712255</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6159,7 +6173,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6169,7 +6183,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Minst 14 ex på mindre yta.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6196,59 +6215,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128827411</v>
+        <v>128826691</v>
       </c>
       <c r="B48" t="n">
-        <v>98669</v>
+        <v>5177</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>542092</v>
+        <v>541964</v>
       </c>
       <c r="R48" t="n">
-        <v>6712255</v>
+        <v>6712107</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6280,7 +6285,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6290,12 +6295,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 14 ex på mindre yta.</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6325,7 +6325,7 @@
         <v>128829197</v>
       </c>
       <c r="B49" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>128570551</v>
       </c>
       <c r="B50" t="n">
-        <v>86872</v>
+        <v>86879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -4057,7 +4057,7 @@
         <v>128827016</v>
       </c>
       <c r="B30" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>128556421</v>
       </c>
       <c r="B31" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>128829012</v>
       </c>
       <c r="B32" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>128827575</v>
       </c>
       <c r="B33" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>128822696</v>
       </c>
       <c r="B34" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>128828742</v>
       </c>
       <c r="B35" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>128827098</v>
       </c>
       <c r="B36" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>128830117</v>
       </c>
       <c r="B37" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>128827330</v>
       </c>
       <c r="B38" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>128828662</v>
       </c>
       <c r="B39" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>128827353</v>
       </c>
       <c r="B40" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>128568945</v>
       </c>
       <c r="B41" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>128563445</v>
       </c>
       <c r="B42" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>128828897</v>
       </c>
       <c r="B43" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>128563536</v>
       </c>
       <c r="B44" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>128828808</v>
       </c>
       <c r="B45" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>128827283</v>
       </c>
       <c r="B46" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>128827411</v>
       </c>
       <c r="B47" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>128829197</v>
       </c>
       <c r="B49" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>128570551</v>
       </c>
       <c r="B50" t="n">
-        <v>86879</v>
+        <v>86881</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -4883,7 +4883,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128830117</v>
+        <v>128827330</v>
       </c>
       <c r="B37" t="n">
         <v>98678</v>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4932,10 +4932,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>542160</v>
+        <v>542092</v>
       </c>
       <c r="R37" t="n">
-        <v>6712167</v>
+        <v>6712260</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4977,7 +4977,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Minst 50 plantor som växer tätt på en yta om cirka 1x1 meter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5004,7 +5009,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128827330</v>
+        <v>128830117</v>
       </c>
       <c r="B38" t="n">
         <v>98678</v>
@@ -5034,7 +5039,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5053,10 +5058,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>542092</v>
+        <v>542160</v>
       </c>
       <c r="R38" t="n">
-        <v>6712260</v>
+        <v>6712167</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5088,7 +5093,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5098,12 +5103,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 50 plantor som växer tätt på en yta om cirka 1x1 meter</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5130,7 +5130,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128828662</v>
+        <v>128827353</v>
       </c>
       <c r="B39" t="n">
         <v>98678</v>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>542178</v>
+        <v>542091</v>
       </c>
       <c r="R39" t="n">
-        <v>6712173</v>
+        <v>6712256</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5251,7 +5251,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128827353</v>
+        <v>128828662</v>
       </c>
       <c r="B40" t="n">
         <v>98678</v>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5300,10 +5300,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>542091</v>
+        <v>542178</v>
       </c>
       <c r="R40" t="n">
-        <v>6712256</v>
+        <v>6712173</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5372,7 +5372,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128568945</v>
+        <v>128563445</v>
       </c>
       <c r="B41" t="n">
         <v>98678</v>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5410,16 +5410,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>542191</v>
+        <v>542085</v>
       </c>
       <c r="R41" t="n">
-        <v>6712170</v>
+        <v>6712250</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5451,7 +5456,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5461,7 +5466,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Minst femton friska bladrosetter.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5488,7 +5498,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128563445</v>
+        <v>128568945</v>
       </c>
       <c r="B42" t="n">
         <v>98678</v>
@@ -5518,7 +5528,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5526,21 +5536,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>542085</v>
+        <v>542191</v>
       </c>
       <c r="R42" t="n">
-        <v>6712250</v>
+        <v>6712170</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5572,7 +5577,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5582,12 +5587,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Minst femton friska bladrosetter.</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6089,59 +6089,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128827411</v>
+        <v>128826691</v>
       </c>
       <c r="B47" t="n">
-        <v>98678</v>
+        <v>5177</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>542092</v>
+        <v>541964</v>
       </c>
       <c r="R47" t="n">
-        <v>6712255</v>
+        <v>6712107</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6173,7 +6159,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6183,12 +6169,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Minst 14 ex på mindre yta.</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6215,45 +6196,59 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128826691</v>
+        <v>128827411</v>
       </c>
       <c r="B48" t="n">
-        <v>5177</v>
+        <v>98678</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541964</v>
+        <v>542092</v>
       </c>
       <c r="R48" t="n">
-        <v>6712107</v>
+        <v>6712255</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6285,7 +6280,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6295,7 +6290,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Minst 14 ex på mindre yta.</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -4883,7 +4883,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128827330</v>
+        <v>128830117</v>
       </c>
       <c r="B37" t="n">
         <v>98678</v>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4932,10 +4932,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>542092</v>
+        <v>542160</v>
       </c>
       <c r="R37" t="n">
-        <v>6712260</v>
+        <v>6712167</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4977,12 +4977,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Minst 50 plantor som växer tätt på en yta om cirka 1x1 meter</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5009,7 +5004,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128830117</v>
+        <v>128827330</v>
       </c>
       <c r="B38" t="n">
         <v>98678</v>
@@ -5039,7 +5034,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5058,10 +5053,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>542160</v>
+        <v>542092</v>
       </c>
       <c r="R38" t="n">
-        <v>6712167</v>
+        <v>6712260</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5093,7 +5088,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5103,7 +5098,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 50 plantor som växer tätt på en yta om cirka 1x1 meter</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -6089,45 +6089,59 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128826691</v>
+        <v>128827411</v>
       </c>
       <c r="B47" t="n">
-        <v>5177</v>
+        <v>98678</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541964</v>
+        <v>542092</v>
       </c>
       <c r="R47" t="n">
-        <v>6712107</v>
+        <v>6712255</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6159,7 +6173,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6169,7 +6183,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Minst 14 ex på mindre yta.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6196,59 +6215,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128827411</v>
+        <v>128826691</v>
       </c>
       <c r="B48" t="n">
-        <v>98678</v>
+        <v>5177</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>542092</v>
+        <v>541964</v>
       </c>
       <c r="R48" t="n">
-        <v>6712255</v>
+        <v>6712107</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6280,7 +6285,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6290,12 +6295,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 14 ex på mindre yta.</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -4057,7 +4057,7 @@
         <v>128827016</v>
       </c>
       <c r="B30" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>128556421</v>
       </c>
       <c r="B31" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>128829012</v>
       </c>
       <c r="B32" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>128827575</v>
       </c>
       <c r="B33" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>128822696</v>
       </c>
       <c r="B34" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>128828742</v>
       </c>
       <c r="B35" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>128827098</v>
       </c>
       <c r="B36" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>128830117</v>
       </c>
       <c r="B37" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>128827330</v>
       </c>
       <c r="B38" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5130,10 +5130,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128827353</v>
+        <v>128828662</v>
       </c>
       <c r="B39" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>542091</v>
+        <v>542178</v>
       </c>
       <c r="R39" t="n">
-        <v>6712256</v>
+        <v>6712173</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5251,10 +5251,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128828662</v>
+        <v>128827353</v>
       </c>
       <c r="B40" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5300,10 +5300,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>542178</v>
+        <v>542091</v>
       </c>
       <c r="R40" t="n">
-        <v>6712173</v>
+        <v>6712256</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5372,10 +5372,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128563445</v>
+        <v>128568945</v>
       </c>
       <c r="B41" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5410,21 +5410,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>542085</v>
+        <v>542191</v>
       </c>
       <c r="R41" t="n">
-        <v>6712250</v>
+        <v>6712170</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5456,7 +5451,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5466,12 +5461,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Minst femton friska bladrosetter.</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5498,10 +5488,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128568945</v>
+        <v>128563445</v>
       </c>
       <c r="B42" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5528,7 +5518,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5536,16 +5526,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>542191</v>
+        <v>542085</v>
       </c>
       <c r="R42" t="n">
-        <v>6712170</v>
+        <v>6712250</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5577,7 +5572,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5587,7 +5582,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Minst femton friska bladrosetter.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5617,7 +5617,7 @@
         <v>128828897</v>
       </c>
       <c r="B43" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5740,10 +5740,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128563536</v>
+        <v>128828808</v>
       </c>
       <c r="B44" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5768,17 +5768,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>542088</v>
+        <v>542185</v>
       </c>
       <c r="R44" t="n">
-        <v>6712247</v>
+        <v>6712179</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5805,22 +5819,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5840,17 +5854,17 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128828808</v>
+        <v>128827283</v>
       </c>
       <c r="B45" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5877,7 +5891,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5892,14 +5906,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>542185</v>
+        <v>542093</v>
       </c>
       <c r="R45" t="n">
-        <v>6712179</v>
+        <v>6712261</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5931,7 +5945,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5941,7 +5955,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5968,10 +5982,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128827283</v>
+        <v>128563536</v>
       </c>
       <c r="B46" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5996,31 +6010,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542093</v>
+        <v>542088</v>
       </c>
       <c r="R46" t="n">
-        <v>6712261</v>
+        <v>6712247</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6047,22 +6047,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6082,66 +6082,52 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128827411</v>
+        <v>128826691</v>
       </c>
       <c r="B47" t="n">
-        <v>98678</v>
+        <v>5177</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>542092</v>
+        <v>541964</v>
       </c>
       <c r="R47" t="n">
-        <v>6712255</v>
+        <v>6712107</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6173,7 +6159,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6183,12 +6169,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Minst 14 ex på mindre yta.</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6215,45 +6196,59 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128826691</v>
+        <v>128827411</v>
       </c>
       <c r="B48" t="n">
-        <v>5177</v>
+        <v>98704</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541964</v>
+        <v>542092</v>
       </c>
       <c r="R48" t="n">
-        <v>6712107</v>
+        <v>6712255</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6285,7 +6280,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6295,7 +6290,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Minst 14 ex på mindre yta.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6325,7 +6325,7 @@
         <v>128829197</v>
       </c>
       <c r="B49" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>128570551</v>
       </c>
       <c r="B50" t="n">
-        <v>86881</v>
+        <v>86882</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -4057,7 +4057,7 @@
         <v>128827016</v>
       </c>
       <c r="B30" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>128556421</v>
       </c>
       <c r="B31" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>128829012</v>
       </c>
       <c r="B32" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>128827575</v>
       </c>
       <c r="B33" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>128822696</v>
       </c>
       <c r="B34" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>128828742</v>
       </c>
       <c r="B35" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>128827098</v>
       </c>
       <c r="B36" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>128830117</v>
       </c>
       <c r="B37" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>128827330</v>
       </c>
       <c r="B38" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>128828662</v>
       </c>
       <c r="B39" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>128827353</v>
       </c>
       <c r="B40" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>128568945</v>
       </c>
       <c r="B41" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>128563445</v>
       </c>
       <c r="B42" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>128828897</v>
       </c>
       <c r="B43" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5740,10 +5740,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128828808</v>
+        <v>128563536</v>
       </c>
       <c r="B44" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5768,31 +5768,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>542185</v>
+        <v>542088</v>
       </c>
       <c r="R44" t="n">
-        <v>6712179</v>
+        <v>6712247</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5819,22 +5805,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5854,17 +5840,17 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128827283</v>
+        <v>128828808</v>
       </c>
       <c r="B45" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5891,7 +5877,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5906,14 +5892,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>542093</v>
+        <v>542185</v>
       </c>
       <c r="R45" t="n">
-        <v>6712261</v>
+        <v>6712179</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5945,7 +5931,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5955,7 +5941,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5982,10 +5968,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128563536</v>
+        <v>128827283</v>
       </c>
       <c r="B46" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6010,17 +5996,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542088</v>
+        <v>542093</v>
       </c>
       <c r="R46" t="n">
-        <v>6712247</v>
+        <v>6712261</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6047,22 +6047,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6199,7 +6199,7 @@
         <v>128827411</v>
       </c>
       <c r="B48" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>128829197</v>
       </c>
       <c r="B49" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -4057,7 +4057,7 @@
         <v>128827016</v>
       </c>
       <c r="B30" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>128556421</v>
       </c>
       <c r="B31" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>128829012</v>
       </c>
       <c r="B32" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>128827575</v>
       </c>
       <c r="B33" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>128822696</v>
       </c>
       <c r="B34" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>128828742</v>
       </c>
       <c r="B35" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>128827098</v>
       </c>
       <c r="B36" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>128830117</v>
       </c>
       <c r="B37" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>128827330</v>
       </c>
       <c r="B38" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>128828662</v>
       </c>
       <c r="B39" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>128827353</v>
       </c>
       <c r="B40" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>128568945</v>
       </c>
       <c r="B41" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>128563445</v>
       </c>
       <c r="B42" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>128828897</v>
       </c>
       <c r="B43" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5740,10 +5740,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128563536</v>
+        <v>128828808</v>
       </c>
       <c r="B44" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5768,17 +5768,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>542088</v>
+        <v>542185</v>
       </c>
       <c r="R44" t="n">
-        <v>6712247</v>
+        <v>6712179</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5805,22 +5819,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5840,17 +5854,17 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åsa Weinberg</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128828808</v>
+        <v>128827283</v>
       </c>
       <c r="B45" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5877,7 +5891,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5892,14 +5906,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kroken, Kroken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>542185</v>
+        <v>542093</v>
       </c>
       <c r="R45" t="n">
-        <v>6712179</v>
+        <v>6712261</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5931,7 +5945,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5941,7 +5955,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5968,10 +5982,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128827283</v>
+        <v>128563536</v>
       </c>
       <c r="B46" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5996,31 +6010,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Kroken, Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542093</v>
+        <v>542088</v>
       </c>
       <c r="R46" t="n">
-        <v>6712261</v>
+        <v>6712247</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6047,22 +6047,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Åsa Weinberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6199,7 +6199,7 @@
         <v>128827411</v>
       </c>
       <c r="B48" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>128829197</v>
       </c>
       <c r="B49" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 41484-2025 artfynd.xlsx
+++ b/artfynd/A 41484-2025 artfynd.xlsx
@@ -6451,7 +6451,7 @@
         <v>128570551</v>
       </c>
       <c r="B50" t="n">
-        <v>86882</v>
+        <v>86885</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
